--- a/05AnalysisOutputs/SpDynLM_Coefficients_Temp2016_052725.xlsx
+++ b/05AnalysisOutputs/SpDynLM_Coefficients_Temp2016_052725.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpkamakura\Documents\01GCOOS\HoustonGalvestonHeat\05AnalysisOutputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{092B14DE-953F-4239-92C1-E15F1D263E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9352DD-6B2E-4FD4-90C4-33591E7F353F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{72AD0371-742B-4676-944D-44F634872100}"/>
+    <workbookView xWindow="4932" yWindow="2256" windowWidth="18156" windowHeight="11460" activeTab="2" xr2:uid="{72AD0371-742B-4676-944D-44F634872100}"/>
   </bookViews>
   <sheets>
     <sheet name="SpDynLM_Coefficients_Temp2016_0" sheetId="1" r:id="rId1"/>
@@ -904,6 +904,102 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:errBars>
+            <c:errBarType val="both"/>
+            <c:errValType val="cust"/>
+            <c:noEndCap val="0"/>
+            <c:plus>
+              <c:numRef>
+                <c:f>Dist2Ocean!$D$2:$D$11</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="10"/>
+                  <c:pt idx="0">
+                    <c:v>1.6900000000000001E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>7.3099999999999999E-4</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>7.3800000000000005E-4</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>8.5400000000000005E-4</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>1.5499999999999999E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>1.9599999999999999E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>1.49E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>1.6800000000000001E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>7.0600000000000003E-4</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>1.7799999999999999E-3</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:plus>
+            <c:minus>
+              <c:numRef>
+                <c:f>Dist2Ocean!$D$2:$D$11</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="10"/>
+                  <c:pt idx="0">
+                    <c:v>1.6900000000000001E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>7.3099999999999999E-4</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>7.3800000000000005E-4</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>8.5400000000000005E-4</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>1.5499999999999999E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>1.9599999999999999E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>1.49E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>1.6800000000000001E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>7.0600000000000003E-4</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>1.7799999999999999E-3</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:minus>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
           <c:cat>
             <c:numRef>
               <c:f>Dist2Ocean!$B$2:$B$11</c:f>
@@ -1056,6 +1152,7 @@
         <c:axId val="1589187263"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="3.5000000000000003E-2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1293,6 +1390,102 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:errBars>
+            <c:errBarType val="both"/>
+            <c:errValType val="cust"/>
+            <c:noEndCap val="0"/>
+            <c:plus>
+              <c:numRef>
+                <c:f>Urban!$D$2:$D$11</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="10"/>
+                  <c:pt idx="0">
+                    <c:v>0.128</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0.123</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0.155</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>0.184</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>0.20899999999999999</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>0.22500000000000001</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>0.23799999999999999</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>0.26700000000000002</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>0.27100000000000002</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>0.26700000000000002</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:plus>
+            <c:minus>
+              <c:numRef>
+                <c:f>Urban!$D$2:$D$11</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="10"/>
+                  <c:pt idx="0">
+                    <c:v>0.128</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0.123</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0.155</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>0.184</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>0.20899999999999999</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>0.22500000000000001</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>0.23799999999999999</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>0.26700000000000002</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>0.27100000000000002</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>0.26700000000000002</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:minus>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
           <c:cat>
             <c:numRef>
               <c:f>Urban!$B$2:$B$11</c:f>
